--- a/out/Attention-Mamba1_repeat_2_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>5.047630813187694</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1128374620163212</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1128374620163212</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>5.047630813187694</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>5.047630813187694</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0003717313721624669</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.4784470219912237</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>5.047630813187694</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>0.9577999177788906</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1104931803046258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1128374620163212</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3675821103144356</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1128374620163212</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.3675821103144356</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4449193865917556</v>
+        <v>0.3671725293803832</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1772475510753914</v>
+        <v>1.258321209199397</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7997677552289364</v>
+        <v>2.886320559411504</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.03391438383100253</v>
+        <v>0.2407655850527431</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>4.447630813187694</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6900899886908326</v>
+        <v>2.107694246770513</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.05940404211870466</v>
+        <v>0.4217235384313109</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>5.047630813187694</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7750007491468555</v>
+        <v>2.710494195498122</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03253181521268202</v>
+        <v>0.2309511564157677</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>5.047630813187694</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7806091762714192</v>
+        <v>2.750309511202405</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01343631026435255</v>
+        <v>0.09538619100777176</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1128374620163212</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7749154010807534</v>
+        <v>2.709888544972271</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01673999914283963</v>
+        <v>0.1188434989243666</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.047630813187694</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7949623259828482</v>
+        <v>2.8522049684017</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01007853189134985</v>
+        <v>0.07155854705596984</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.798368749897749</v>
+        <v>2.876399098640428</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.007661124480064697</v>
+        <v>0.05440373272168264</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>5.047630813187694</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8036090210412259</v>
+        <v>2.913618054960181</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003384959975843988</v>
+        <v>0.02406370695563873</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8027139994397545</v>
+        <v>2.907291955447496</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002686200004741752</v>
+        <v>0.01909473268025716</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.804698873332979</v>
+        <v>2.921409047413114</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00132828898034159</v>
+        <v>0.009465604276872907</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.447630813187694</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8046700566772944</v>
+        <v>2.921234999875282</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0007717565990830875</v>
+        <v>0.005502117011476722</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8048820738816373</v>
+        <v>2.922769035680451</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0003819236991687289</v>
+        <v>0.002750013106111175</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8048765921355123</v>
+        <v>2.922760605503156</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001876014268795741</v>
+        <v>0.001354708580806545</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8048667166238537</v>
+        <v>2.922721151252127</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001051425416707903</v>
+        <v>0.0007860237083629485</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7128374620163211</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8048926386853107</v>
+        <v>2.9229348986653</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.294349193752244e-05</v>
+        <v>0.0002583724734486851</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.804849952564216</v>
+        <v>2.922667205637213</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.296632917816834e-05</v>
+        <v>0.0001275016776889915</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8048451652032432</v>
+        <v>2.922663685635094</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.784784520434025e-06</v>
+        <v>6.838588390325518e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.80484195875155</v>
+        <v>2.92267063240421</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>3.055270670444892e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8048365722673925</v>
+        <v>2.922663304575616</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>1.536440521940679e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8048331876489415</v>
+        <v>2.922666374239059</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>-2.422504053549707e-06</v>
+        <v>5.309983785801169e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8048275202186678</v>
+        <v>2.922658704517965</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8048279007537256</v>
+        <v>2.922655219297657</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8048281290747602</v>
+        <v>2.922650671985472</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8048282190194102</v>
+        <v>2.922650761930122</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8048273610858254</v>
+        <v>2.922649903996537</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8048275894068601</v>
+        <v>2.922650132317572</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8048267937426483</v>
+        <v>2.92264933665336</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8048268560120214</v>
+        <v>2.922649398922732</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8048268836872983</v>
+        <v>2.92264942659801</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8048270359013215</v>
+        <v>2.922649578812032</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8048266899603598</v>
+        <v>2.922649232871071</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8048267660673715</v>
+        <v>2.922649308978083</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8048269321190331</v>
+        <v>2.922649475029744</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8048272918976331</v>
+        <v>2.922649834808344</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8048273126540908</v>
+        <v>2.922649855564802</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8048274164363793</v>
+        <v>2.92264995934709</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.804827644757414</v>
+        <v>2.922650187668125</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8048275202186678</v>
+        <v>2.922650063129379</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8048275478939446</v>
+        <v>2.922650090804656</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8048276032444986</v>
+        <v>2.92265014615521</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8048278661596293</v>
+        <v>2.92265040907034</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8048277831337985</v>
+        <v>2.92265032604451</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8048275755692218</v>
+        <v>2.922650118479933</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8048275894068601</v>
+        <v>2.922650132317572</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8048277277832449</v>
+        <v>2.922650270693956</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8048274441116562</v>
+        <v>2.922649987022367</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8048272711411754</v>
+        <v>2.922649814051887</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8048271673588869</v>
+        <v>2.922649710269598</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8048273126540908</v>
+        <v>2.922649855564802</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.804827554812764</v>
+        <v>2.922650097723475</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8048273818422831</v>
+        <v>2.922649924752994</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8048270843330562</v>
+        <v>2.922649627243767</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8048270704954176</v>
+        <v>2.922649613406129</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8048267037979984</v>
+        <v>2.922649246708709</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8048267037979984</v>
+        <v>2.922649246708709</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8048266415286253</v>
+        <v>2.922649184439337</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8048265377463367</v>
+        <v>2.922649080657048</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.804826364775856</v>
+        <v>2.922648907686567</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8048264132075906</v>
+        <v>2.922648956118302</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8048260534289905</v>
+        <v>2.922648596339702</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8048260119160752</v>
+        <v>2.922648554826786</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8048260672666289</v>
+        <v>2.92264861017734</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8048261226171828</v>
+        <v>2.922648665527894</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8048261641300982</v>
+        <v>2.92264870704081</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8048258942961481</v>
+        <v>2.922648437206859</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8048259496467021</v>
+        <v>2.922648492557413</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8048260949419059</v>
+        <v>2.922648637852617</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8048260603478097</v>
+        <v>2.922648603258521</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8048260465101712</v>
+        <v>2.922648589420882</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8048261364548214</v>
+        <v>2.922648679365532</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.804826454720506</v>
+        <v>2.922648997631217</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8048262748312058</v>
+        <v>2.922648817741917</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8048263163441213</v>
+        <v>2.922648859254832</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.804826129536002</v>
+        <v>2.922648672446713</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8048261987241945</v>
+        <v>2.922648741634905</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8048259980784366</v>
+        <v>2.922648540989148</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.804826039591352</v>
+        <v>2.922648582502063</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8048260672666289</v>
+        <v>2.92264861017734</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>5.047630813187694</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1128374620163212</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1128374620163212</v>
+        <v>-0.1230885453826203</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.1230885453826203</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>5.047630813187694</v>
+        <v>1.985637151539127</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>5.047630813187694</v>
+        <v>3.04</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0004489591195912799</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.5778453591463517</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>5.047630813187694</v>
+        <v>1.985637151539127</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>1.156784279671967</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1334482447377539</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1128374620163212</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.4439481552890069</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1128374620163212</v>
+        <v>-0.1230885453826203</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.4439481552890069</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4449193865917556</v>
+        <v>0.443843075725578</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1772475510753914</v>
+        <v>0.3228269820701725</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7997677552289364</v>
+        <v>1.09014018902541</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.03391438383100253</v>
+        <v>0.06176936761324733</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>4.447630813187694</v>
+        <v>1.785637151539126</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6900899886908326</v>
+        <v>0.8903805143678687</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.05940404211870466</v>
+        <v>0.1081949054634147</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>5.047630813187694</v>
+        <v>3.04</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7750007491468555</v>
+        <v>1.045031236550437</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.03253181521268202</v>
+        <v>0.05925146750882677</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>5.047630813187694</v>
+        <v>1.985637151539127</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7806091762714192</v>
+        <v>1.055246008633491</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01343631026435255</v>
+        <v>0.02447152216595277</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1128374620163212</v>
+        <v>1.985637151539127</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7749154010807534</v>
+        <v>1.044875865446427</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01673999914283963</v>
+        <v>0.03048941661423625</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>5.047630813187694</v>
+        <v>0.9312743030782531</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7949623259828482</v>
+        <v>1.081387872044009</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01007853189134985</v>
+        <v>0.01835915778434088</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7128374620163211</v>
+        <v>1.985637151539127</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.798368749897749</v>
+        <v>1.087595099399717</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.007661124480064697</v>
+        <v>0.0139564373879969</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>5.047630813187694</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8036090210412259</v>
+        <v>1.09714332873356</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.003384959975843988</v>
+        <v>0.006170988966774374</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8027139994397545</v>
+        <v>1.095517223554296</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002686200004741752</v>
+        <v>0.004895657553152038</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.804698873332979</v>
+        <v>1.09913577085939</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00132828898034159</v>
+        <v>0.002423937335669201</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>4.447630813187694</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8046700566772944</v>
+        <v>1.099087399599838</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0007717565990830875</v>
+        <v>0.001408871562375957</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7128374620163211</v>
+        <v>0.731274303078253</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8048820738816373</v>
+        <v>1.099477419679652</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0003819236991687289</v>
+        <v>0.0007019357811879784</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8048765921355123</v>
+        <v>1.099471539496883</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001876014268795741</v>
+        <v>0.000342832427648186</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8048667166238537</v>
+        <v>1.099457699874269</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001051425416707903</v>
+        <v>0.0001985968194520669</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8048926386853107</v>
+        <v>1.099509001951077</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>3.294349193752244e-05</v>
+        <v>6.195910341915722e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.804849952564216</v>
+        <v>1.099436390020421</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.296632917816834e-05</v>
+        <v>2.868686720906565e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8048451652032432</v>
+        <v>1.099431776610664</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.784784520434025e-06</v>
+        <v>1.456956904086805e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.80484195875155</v>
+        <v>1.099429962415761</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8048365722673925</v>
+        <v>1.09942434166147</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8048331876489415</v>
+        <v>1.099421493088767</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8048275202186678</v>
+        <v>1.099415825658494</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8048279007537256</v>
+        <v>1.099416206193552</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8048281290747602</v>
+        <v>1.099416434514586</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8048282190194102</v>
+        <v>1.099416524459236</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8048273610858254</v>
+        <v>1.099415666525651</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8048275894068601</v>
+        <v>1.099415894846686</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8048267937426483</v>
+        <v>1.099415099182474</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8048268560120214</v>
+        <v>1.099415161451847</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8048268836872983</v>
+        <v>1.099415189127124</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8048270359013215</v>
+        <v>1.099415341341147</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8048266899603598</v>
+        <v>1.099414995400186</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8048267660673715</v>
+        <v>1.099415071507197</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8048269321190331</v>
+        <v>1.099415237558859</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8048272918976331</v>
+        <v>1.099415597337459</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8048273126540908</v>
+        <v>1.099415618093917</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8048274164363793</v>
+        <v>1.099415721876205</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.804827644757414</v>
+        <v>1.09941595019724</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8048275202186678</v>
+        <v>1.099415825658494</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8048275478939446</v>
+        <v>1.099415853333771</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8048276032444986</v>
+        <v>1.099415908684324</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8048278661596293</v>
+        <v>1.099416171599455</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8048277831337985</v>
+        <v>1.099416088573624</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8048275755692218</v>
+        <v>1.099415881009047</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8048275894068601</v>
+        <v>1.099415894846686</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8048277277832449</v>
+        <v>1.099416033223071</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8048274441116562</v>
+        <v>1.099415749551482</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8048272711411754</v>
+        <v>1.099415576581001</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8048271673588869</v>
+        <v>1.099415472798713</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8048273126540908</v>
+        <v>1.099415618093917</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.804827554812764</v>
+        <v>1.09941586025259</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8048273818422831</v>
+        <v>1.099415687282109</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8048270843330562</v>
+        <v>1.099415389772882</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8048270704954176</v>
+        <v>1.099415375935243</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8048267037979984</v>
+        <v>1.099415009237824</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8048267037979984</v>
+        <v>1.099415009237824</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8048266415286253</v>
+        <v>1.099414946968451</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8048265377463367</v>
+        <v>1.099414843186162</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.804826364775856</v>
+        <v>1.099414670215682</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8048264132075906</v>
+        <v>1.099414718647416</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8048260534289905</v>
+        <v>1.099414358868816</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8048260119160752</v>
+        <v>1.099414317355901</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8048260672666289</v>
+        <v>1.099414372706455</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8048261226171828</v>
+        <v>1.099414428057009</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8048261641300982</v>
+        <v>1.099414469569924</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8048258942961481</v>
+        <v>1.099414199735974</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8048259496467021</v>
+        <v>1.099414255086528</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8048260949419059</v>
+        <v>1.099414400381732</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8048260603478097</v>
+        <v>1.099414365787636</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8048260465101712</v>
+        <v>1.099414351949997</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8048261364548214</v>
+        <v>1.099414441894647</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.804826454720506</v>
+        <v>1.099414760160332</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8048262748312058</v>
+        <v>1.099414580271032</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8048263163441213</v>
+        <v>1.099414621783947</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.804826129536002</v>
+        <v>1.099414434975828</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8048261987241945</v>
+        <v>1.09941450416402</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8048259980784366</v>
+        <v>1.099414303518263</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.804826039591352</v>
+        <v>1.099414345031178</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7128374620163211</v>
+        <v>-0.3230885453826203</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8048260672666289</v>
+        <v>1.099414372706455</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00687824934720993</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.007505979388952255</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.006307195872068405</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.005151443183422089</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.006475754082202911</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005930587649345398</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.007545549422502518</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.005064573138952255</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.004910707473754883</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.006354920566082001</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.007699910551309586</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.008261155337095261</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.006518315523862839</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.007455531507730484</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.007861923426389694</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.007971353828907013</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.007098883390426636</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.00602935254573822</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.004527539014816284</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.005756601691246033</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.006215587258338928</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.007289383560419083</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.007118146866559982</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.005237732082605362</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.006490688771009445</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.004283234477043152</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.9312743030782531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001071128994226456</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.9312743030782531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.00246182456612587</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.9312743030782531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.004014022648334503</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.003960978239774704</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.005176752805709839</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.005913928151130676</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005282577127218246</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.00199403241276741</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.003639750182628632</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.003826282918453217</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003140386193990707</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004195313900709152</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.003768943250179291</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.002684872597455978</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001132059842348099</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9312743030782531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0001547075808048248</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.985637151539127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.00349707156419754</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004489591195912799</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5778453591463517</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002369079738855362</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.985637151539127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.156784279671967</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1334482447377539</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0007431060075759888</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9312743030782531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4439481552890069</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0001879595220088959</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1230885453826203</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4439481552890069</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0003432594239711761</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.443843075725578</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.3228269820701725</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001090951263904572</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.09014018902541</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.06176936761324733</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001334656029939651</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.785637151539126</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8903805143678687</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1081949054634147</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0003335066139698029</v>
       </c>
       <c r="JB51" t="n">
-        <v>3.04</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.045031236550437</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.05925146750882677</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001070287078619003</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.985637151539127</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.055246008633491</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.02447152216595277</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001078221946954727</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.985637151539127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.044875865446427</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03048941661423625</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.003015611320734024</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9312743030782531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.081387872044009</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01835915778434088</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002065412700176239</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.985637151539127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.087595099399717</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0139564373879969</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.003884349018335342</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.09714332873356</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.006170988966774374</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005820896476507187</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.095517223554296</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.004895657553152038</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.007255874574184418</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.09913577085939</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.002423937335669201</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001701094210147858</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.099087399599838</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001408871562375957</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.007242858409881592</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.731274303078253</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.099477419679652</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0007019357811879784</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.007534090429544449</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.099471539496883</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000342832427648186</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.008805092424154282</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.099457699874269</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001985968194520669</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007196448743343353</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.099509001951077</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.195910341915722e-05</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.006037227809429169</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.099436390020421</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.868686720906565e-05</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.004034660756587982</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.099431776610664</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.456956904086805e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.005281966179609299</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.099429962415761</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.003626327961683273</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.09942434166147</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003282453864812851</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.099421493088767</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004902791231870651</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.099415825658494</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004463009536266327</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.099416206193552</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007225818932056427</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.099416434514586</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00508030503988266</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.099416524459236</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.005166396498680115</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.099415666525651</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002670217305421829</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.099415894846686</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002564720809459686</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.099415099182474</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003532987087965012</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.099415161451847</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003161296248435974</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.099415189127124</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002089496701955795</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.099415341341147</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003485914319753647</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.099414995400186</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003165960311889648</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.099415071507197</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004386305809020996</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.099415237558859</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002550065517425537</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.099415597337459</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002520624548196793</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.099415618093917</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002667535096406937</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.099415721876205</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005533874034881592</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.09941595019724</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.005582679063081741</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.099415825658494</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006209712475538254</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.099415853333771</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004277806729078293</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.099415908684324</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.005710151046514511</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.099416171599455</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00532015785574913</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.099416088573624</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.005722451955080032</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.099415881009047</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005747728049755096</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.099415894846686</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005707427859306335</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.099416033223071</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.005340438336133957</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.099415749551482</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.005299773067235947</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.099415576581001</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003984715789556503</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.099415472798713</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.004901308566331863</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.099415618093917</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005383327603340149</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.09941586025259</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.004712961614131927</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.099415687282109</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00517808273434639</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.099415389772882</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.00393788143992424</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.099415375935243</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004466038197278976</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.099415009237824</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003849580883979797</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.099415009237824</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002238687127828598</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.099414946968451</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004118509590625763</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.099414843186162</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003761321306228638</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.099414670215682</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003349609673023224</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.099414718647416</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003793500363826752</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.099414358868816</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004159517586231232</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.099414317355901</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003385767340660095</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.099414372706455</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004365429282188416</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.099414428057009</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004116564989089966</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.099414469569924</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.00436687096953392</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.099414199735974</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004358567297458649</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.099414255086528</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004366636276245117</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.099414400381732</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.0044383704662323</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.099414365787636</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00455678254365921</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.099414351949997</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003391735255718231</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.099414441894647</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.000871412456035614</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.099414760160332</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003466937690973282</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.099414580271032</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003490697592496872</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.099414621783947</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003852680325508118</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.099414434975828</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004107560962438583</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3230885453826203</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.09941450416402</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003817304968833923</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.099414303518263</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004347115755081177</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.5100000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.099414345031178</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003908224403858185</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3230885453826203</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.099414372706455</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.00687824934720993</v>
+        <v>-0.006878253072500229</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.007505979388952255</v>
+        <v>-0.007505998015403748</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.005151443183422089</v>
+        <v>-0.005151472985744476</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.006475754082202911</v>
+        <v>-0.006475776433944702</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.005930587649345398</v>
+        <v>-0.005930602550506592</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.007545549422502518</v>
+        <v>-0.007545575499534607</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.005064573138952255</v>
+        <v>-0.005064588040113449</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.004910707473754883</v>
+        <v>-0.004910696297883987</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.006354920566082001</v>
+        <v>-0.006354872137308121</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.008261155337095261</v>
+        <v>-0.008261144161224365</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.006518315523862839</v>
+        <v>-0.006518330425024033</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.007455531507730484</v>
+        <v>-0.007455524057149887</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.007861923426389694</v>
+        <v>-0.007861878722906113</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.007098883390426636</v>
+        <v>-0.007098875939846039</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.00602935254573822</v>
+        <v>-0.006029371172189713</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.005756601691246033</v>
+        <v>-0.005756594240665436</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.006215587258338928</v>
+        <v>-0.006215546280145645</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.007289383560419083</v>
+        <v>-0.007289394736289978</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.007118146866559982</v>
+        <v>-0.007118124514818192</v>
       </c>
       <c r="JB24" t="n">
         <v>0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.005237732082605362</v>
+        <v>-0.005237709730863571</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.006490688771009445</v>
+        <v>-0.006490670144557953</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.004283234477043152</v>
+        <v>-0.004283204674720764</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001071128994226456</v>
+        <v>0.001071084290742874</v>
       </c>
       <c r="JB28" t="n">
         <v>0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.00246182456612587</v>
+        <v>-0.002461809664964676</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.004014022648334503</v>
+        <v>-0.004014015197753906</v>
       </c>
       <c r="JB30" t="n">
         <v>0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.003960978239774704</v>
+        <v>-0.003960955888032913</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.005176752805709839</v>
+        <v>-0.005176730453968048</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.005913928151130676</v>
+        <v>-0.005913939327001572</v>
       </c>
       <c r="JB33" t="n">
         <v>0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.005282577127218246</v>
+        <v>-0.005282599478960037</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.00199403241276741</v>
+        <v>-0.001994039863348007</v>
       </c>
       <c r="JB35" t="n">
         <v>0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.003826282918453217</v>
+        <v>-0.003826230764389038</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.003140386193990707</v>
+        <v>-0.00314037874341011</v>
       </c>
       <c r="JB38" t="n">
         <v>0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.004195313900709152</v>
+        <v>-0.004195325076580048</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.003768943250179291</v>
+        <v>-0.003768946975469589</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.002684872597455978</v>
+        <v>-0.002684861421585083</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001132059842348099</v>
+        <v>-0.001132067292928696</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0001547075808048248</v>
+        <v>0.0001546964049339294</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.00349707156419754</v>
+        <v>0.00349704921245575</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.002369079738855362</v>
+        <v>0.002369087189435959</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0001879595220088959</v>
+        <v>-0.0001879557967185974</v>
       </c>
       <c r="JB47" t="n">
         <v>0.1199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0003432594239711761</v>
+        <v>-0.0003432929515838623</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001090951263904572</v>
+        <v>-0.00109095498919487</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.001334656029939651</v>
+        <v>0.001334644854068756</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.0003335066139698029</v>
+        <v>0.0003335215151309967</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.001070287078619003</v>
+        <v>0.001070305705070496</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001078221946954727</v>
+        <v>-0.001078210771083832</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.003015611320734024</v>
+        <v>0.003015585243701935</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002065412700176239</v>
+        <v>-0.002065431326627731</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.003884349018335342</v>
+        <v>0.00388433039188385</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.005820896476507187</v>
+        <v>-0.005820903927087784</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.5799999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.007255874574184418</v>
+        <v>-0.007255885750055313</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.5799999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.001701094210147858</v>
+        <v>0.001701090484857559</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.8599999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.007242858409881592</v>
+        <v>-0.007242865860462189</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.8599999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.007534090429544449</v>
+        <v>-0.00753408670425415</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.8599999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.008805092424154282</v>
+        <v>-0.008805066347122192</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.007196448743343353</v>
+        <v>-0.007196437567472458</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.006037227809429169</v>
+        <v>-0.006037198007106781</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.004034660756587982</v>
+        <v>-0.004034671932458878</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.005281966179609299</v>
+        <v>-0.005281988531351089</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.003626327961683273</v>
+        <v>-0.003626346588134766</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003282453864812851</v>
+        <v>-0.003282435238361359</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.004902791231870651</v>
+        <v>-0.004902772605419159</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.004463009536266327</v>
+        <v>-0.004462979733943939</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.007225818932056427</v>
+        <v>-0.007225833833217621</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00508030503988266</v>
+        <v>-0.005080271512269974</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.1199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.005166396498680115</v>
+        <v>-0.005166411399841309</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002670217305421829</v>
+        <v>-0.002670202404260635</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002564720809459686</v>
+        <v>-0.002564709633588791</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
         <v>0.9559177770615876</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003532987087965012</v>
+        <v>-0.003533005714416504</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0.9559178393309608</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003161296248435974</v>
+        <v>-0.003161285072565079</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0.9559178670062376</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002089496701955795</v>
+        <v>-0.002089504152536392</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC78" t="n">
         <v>0.9559180192202609</v>
@@ -63749,7 +63749,7 @@
         <v>-0.003485914319753647</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
         <v>0.9559176732792992</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003165960311889648</v>
+        <v>-0.003165975213050842</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.004386305809020996</v>
+        <v>-0.004386339336633682</v>
       </c>
       <c r="JB81" t="n">
         <v>0.3</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002550065517425537</v>
+        <v>-0.002550054341554642</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0.9559182752165725</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002520624548196793</v>
+        <v>-0.002520617097616196</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002667535096406937</v>
+        <v>-0.002667546272277832</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.3</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.005533874034881592</v>
+        <v>-0.005533859133720398</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.006209712475538254</v>
+        <v>-0.00620969757437706</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.004277806729078293</v>
+        <v>-0.004277776926755905</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.8599999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.005710151046514511</v>
+        <v>-0.005710210651159286</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.00532015785574913</v>
+        <v>-0.005320176482200623</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.8599999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.005722451955080032</v>
+        <v>-0.005722459405660629</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.005747728049755096</v>
+        <v>-0.005747724324464798</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.005707427859306335</v>
+        <v>-0.005707435309886932</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.005340438336133957</v>
+        <v>-0.005340449512004852</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.7199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.005299773067235947</v>
+        <v>-0.005299769341945648</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.1199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.003984715789556503</v>
+        <v>-0.003984685987234116</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.1199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.004901308566331863</v>
+        <v>-0.004901327192783356</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.005383327603340149</v>
+        <v>-0.005383342504501343</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.1199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.004712961614131927</v>
+        <v>-0.004712969064712524</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.1199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.00517808273434639</v>
+        <v>-0.005178093910217285</v>
       </c>
       <c r="JB100" t="n">
         <v>0.02000000000000007</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.00393788143992424</v>
+        <v>-0.003937862813472748</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.004466038197278976</v>
+        <v>-0.004466041922569275</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003849580883979797</v>
+        <v>-0.003849584609270096</v>
       </c>
       <c r="JB103" t="n">
         <v>0.8599999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002238687127828598</v>
+        <v>-0.002238690853118896</v>
       </c>
       <c r="JB104" t="n">
         <v>0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003761321306228638</v>
+        <v>-0.003761310130357742</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003349609673023224</v>
+        <v>-0.003349587321281433</v>
       </c>
       <c r="JB107" t="n">
         <v>0.8599999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003793500363826752</v>
+        <v>-0.003793496638536453</v>
       </c>
       <c r="JB108" t="n">
         <v>0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004159517586231232</v>
+        <v>-0.004159547388553619</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003385767340660095</v>
+        <v>-0.0033857561647892</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.02000000000000007</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.004365429282188416</v>
+        <v>-0.004365421831607819</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.004116564989089966</v>
+        <v>-0.004116557538509369</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.00436687096953392</v>
+        <v>-0.004366893321275711</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.004366636276245117</v>
+        <v>-0.004366625100374222</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.3</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.0044383704662323</v>
+        <v>-0.004438403993844986</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00455678254365921</v>
+        <v>-0.004556771367788315</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003391735255718231</v>
+        <v>-0.003391750156879425</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.000871412456035614</v>
+        <v>-0.0008714273571968079</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003466937690973282</v>
+        <v>-0.003466974943876266</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003490697592496872</v>
+        <v>-0.00349067896604538</v>
       </c>
       <c r="JB121" t="n">
         <v>0.8599999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003817304968833923</v>
+        <v>-0.003817282617092133</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.004347115755081177</v>
+        <v>-0.004347153007984161</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5100000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003908224403858185</v>
+        <v>-0.003908243030309677</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.7200000000000004</v>
